--- a/artfynd/A 57190-2025 artfynd.xlsx
+++ b/artfynd/A 57190-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>99022702</v>
+        <v>99022701</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92123</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>48</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>613277.6511457252</v>
+        <v>613252</v>
       </c>
       <c r="R2" t="n">
-        <v>7240983.723477389</v>
+        <v>7240947</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2021-08-18</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-08-18</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>99022687</v>
+        <v>99022706</v>
       </c>
       <c r="B3" t="n">
-        <v>89745</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92123</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1505</v>
+        <v>48</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kristallticka</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Skeletocutis stellae</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pilát) Jean Keller</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>613298.507108954</v>
+        <v>613280</v>
       </c>
       <c r="R3" t="n">
-        <v>7240987.041669345</v>
+        <v>7240970</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,19 +840,9 @@
           <t>2021-08-18</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-08-18</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,37 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>99022698</v>
+        <v>99022699</v>
       </c>
       <c r="B4" t="n">
-        <v>78603</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6464</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>613233.2134876503</v>
+        <v>613248</v>
       </c>
       <c r="R4" t="n">
-        <v>7240884.342182924</v>
+        <v>7240950</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,19 +937,9 @@
           <t>2021-08-18</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-08-18</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,12 +969,7 @@
         <v>99022705</v>
       </c>
       <c r="B5" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1051,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>613279.8753191422</v>
+        <v>613280</v>
       </c>
       <c r="R5" t="n">
-        <v>7240969.556944153</v>
+        <v>7240970</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1084,19 +1034,9 @@
           <t>2021-08-18</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2021-08-18</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,15 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>99022694</v>
+        <v>99022703</v>
       </c>
       <c r="B6" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1139,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>613141.4881088643</v>
+        <v>613292</v>
       </c>
       <c r="R6" t="n">
-        <v>7240923.151602535</v>
+        <v>7240991</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1196,19 +1131,9 @@
           <t>2021-08-18</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2021-08-18</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,37 +1160,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>99022697</v>
+        <v>99022687</v>
       </c>
       <c r="B7" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92295</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>1505</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kristallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Skeletocutis stellae</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Pilát) Jean Keller</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>613233.1490487346</v>
+        <v>613299</v>
       </c>
       <c r="R7" t="n">
-        <v>7240886.016478711</v>
+        <v>7240987</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1308,19 +1228,9 @@
           <t>2021-08-18</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2021-08-18</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,37 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>99022695</v>
+        <v>99022696</v>
       </c>
       <c r="B8" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221952</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>613150.610372056</v>
+        <v>613156</v>
       </c>
       <c r="R8" t="n">
-        <v>7240915.118665465</v>
+        <v>7240909</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1420,19 +1325,9 @@
           <t>2021-08-18</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2021-08-18</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,15 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>99022708</v>
+        <v>99022697</v>
       </c>
       <c r="B9" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>613281.1324623734</v>
+        <v>613233</v>
       </c>
       <c r="R9" t="n">
-        <v>7240958.706582645</v>
+        <v>7240886</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1532,19 +1422,9 @@
           <t>2021-08-18</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2021-08-18</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,15 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>99022712</v>
+        <v>99022708</v>
       </c>
       <c r="B10" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1587,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1611,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>613308.9353172558</v>
+        <v>613281</v>
       </c>
       <c r="R10" t="n">
-        <v>7240956.004591814</v>
+        <v>7240959</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1644,19 +1519,9 @@
           <t>2021-08-18</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2021-08-18</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,15 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>99022703</v>
+        <v>99022702</v>
       </c>
       <c r="B11" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1699,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1723,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>613291.6410763726</v>
+        <v>613278</v>
       </c>
       <c r="R11" t="n">
-        <v>7240990.96905949</v>
+        <v>7240984</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1756,19 +1616,9 @@
           <t>2021-08-18</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2021-08-18</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1795,37 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>99022711</v>
+        <v>99022712</v>
       </c>
       <c r="B12" t="n">
-        <v>78602</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1835,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>613310.1441277249</v>
+        <v>613309</v>
       </c>
       <c r="R12" t="n">
-        <v>7240957.308702545</v>
+        <v>7240956</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1868,19 +1713,9 @@
           <t>2021-08-18</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2021-08-18</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1907,15 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>99022710</v>
+        <v>99022704</v>
       </c>
       <c r="B13" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1923,21 +1753,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221952</v>
+        <v>6463</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1947,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>613286.0966720999</v>
+        <v>613308</v>
       </c>
       <c r="R13" t="n">
-        <v>7240949.675665983</v>
+        <v>7240981</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1980,19 +1810,9 @@
           <t>2021-08-18</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2021-08-18</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2019,15 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>99022704</v>
+        <v>99022711</v>
       </c>
       <c r="B14" t="n">
-        <v>78602</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2059,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>613307.9680850556</v>
+        <v>613310</v>
       </c>
       <c r="R14" t="n">
-        <v>7240981.118323624</v>
+        <v>7240957</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2092,19 +1907,9 @@
           <t>2021-08-18</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2021-08-18</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2131,37 +1936,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>99022706</v>
+        <v>99022698</v>
       </c>
       <c r="B15" t="n">
-        <v>89577</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>48</v>
+        <v>6464</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Romell) Singer</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2171,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>613279.8753191422</v>
+        <v>613233</v>
       </c>
       <c r="R15" t="n">
-        <v>7240969.556944153</v>
+        <v>7240884</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2204,19 +2004,9 @@
           <t>2021-08-18</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2021-08-18</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2243,37 +2033,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>99022696</v>
+        <v>99022692</v>
       </c>
       <c r="B16" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2081</v>
+        <v>221952</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2283,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>613155.8806118933</v>
+        <v>613204</v>
       </c>
       <c r="R16" t="n">
-        <v>7240909.033523378</v>
+        <v>7240968</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2316,19 +2101,9 @@
           <t>2021-08-18</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2021-08-18</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2355,15 +2130,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>99022692</v>
+        <v>99022695</v>
       </c>
       <c r="B17" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2395,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>613203.9779037205</v>
+        <v>613151</v>
       </c>
       <c r="R17" t="n">
-        <v>7240967.893087614</v>
+        <v>7240915</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2428,19 +2198,9 @@
           <t>2021-08-18</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2021-08-18</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2467,37 +2227,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>99022701</v>
+        <v>99022710</v>
       </c>
       <c r="B18" t="n">
-        <v>89577</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>48</v>
+        <v>221952</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Romell) Singer</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2507,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>613252.1851552761</v>
+        <v>613286</v>
       </c>
       <c r="R18" t="n">
-        <v>7240947.531688148</v>
+        <v>7240950</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2540,19 +2295,9 @@
           <t>2021-08-18</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2021-08-18</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2576,118 +2321,6 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>99022699</v>
-      </c>
-      <c r="B19" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>Juktfors, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q19" t="n">
-        <v>613248.3008428583</v>
-      </c>
-      <c r="R19" t="n">
-        <v>7240950.316461475</v>
-      </c>
-      <c r="S19" t="n">
-        <v>10</v>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>2021-08-18</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>2021-08-18</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT19" t="inlineStr"/>
-      <c r="AW19" t="inlineStr">
-        <is>
-          <t>Jonas Muntlin</t>
-        </is>
-      </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>Jonas Muntlin</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 57190-2025 artfynd.xlsx
+++ b/artfynd/A 57190-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99022701</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99022706</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99022699</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99022705</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99022703</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99022687</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99022696</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99022697</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99022708</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99022702</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99022712</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99022704</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99022711</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99022698</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2127,6 +2202,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99022692</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2224,6 +2304,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99022695</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2321,8 +2406,32 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99022710</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>